--- a/src/test/resources/TestData/GuruBankTestData.xlsx
+++ b/src/test/resources/TestData/GuruBankTestData.xlsx
@@ -9,12 +9,12 @@
   <sheets>
     <sheet name="TestData" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="122211"/>
+  <calcPr calcId="122211" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
   <si>
     <t>Name</t>
   </si>
@@ -116,9 +116,6 @@
   </si>
   <si>
     <t>CustomerId</t>
-  </si>
-  <si>
-    <t>44622</t>
   </si>
   <si>
     <t>37860</t>
@@ -134,7 +131,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <numFmts count="0"/>
   <fonts count="5">
     <font>
       <sz val="11"/>
@@ -539,16 +535,16 @@
   <dimension ref="A1:K4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" bestFit="true" customWidth="true" width="36.42578125"/>
-    <col min="2" max="2" bestFit="true" customWidth="true" width="9.85546875"/>
-    <col min="3" max="3" bestFit="true" customWidth="true" width="15.7109375"/>
-    <col min="4" max="4" bestFit="true" customWidth="true" width="26.140625"/>
-    <col min="5" max="6" bestFit="true" customWidth="true" width="14.28515625"/>
-    <col min="7" max="7" bestFit="true" customWidth="true" width="9.85546875"/>
-    <col min="8" max="8" bestFit="true" customWidth="true" width="14.140625"/>
-    <col min="9" max="9" bestFit="true" customWidth="true" width="32.0"/>
-    <col min="10" max="10" bestFit="true" customWidth="true" width="24.5703125"/>
-    <col min="11" max="11" bestFit="true" customWidth="true" width="11.28515625"/>
+    <col min="1" max="1" width="23.85546875" customWidth="1"/>
+    <col min="2" max="2" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="26.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="25.42578125" customWidth="1"/>
+    <col min="10" max="10" width="24.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11">
@@ -618,7 +614,7 @@
         <v>17</v>
       </c>
       <c r="K2" s="1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:11" ht="15.75">
@@ -653,7 +649,7 @@
         <v>31</v>
       </c>
       <c r="K3" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:11" ht="15.75">
@@ -688,7 +684,7 @@
         <v>32</v>
       </c>
       <c r="K4" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
   </sheetData>
